--- a/Packages/cn.etetet.twsmap/Luban/Config/Datas/GameLevel.xlsx
+++ b/Packages/cn.etetet.twsmap/Luban/Config/Datas/GameLevel.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +50,15 @@
     <t>MapResName</t>
   </si>
   <si>
+    <t>TotalTime</t>
+  </si>
+  <si>
+    <t>*MonsterConfigData</t>
+  </si>
+  <si>
+    <t>FinalMonsterConfigData</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -62,6 +71,15 @@
     <t>(list#sep=,),int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>list,CreateMonsterData</t>
+  </si>
+  <si>
+    <t>CreateMonsterData</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -78,6 +96,15 @@
   </si>
   <si>
     <t>地图资源</t>
+  </si>
+  <si>
+    <t>总时间/s</t>
+  </si>
+  <si>
+    <t>怪物数据配置</t>
+  </si>
+  <si>
+    <t>最终Boss配置</t>
   </si>
   <si>
     <t>疯狂街区</t>
@@ -252,13 +279,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -863,27 +890,28 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1203,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1211,445 +1239,822 @@
     <col min="4" max="4" width="97.25" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="2" customWidth="1"/>
     <col min="6" max="6" width="32.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="7" max="8" width="22.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
+    <col min="12" max="14" width="18.875" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="21" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="21" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="21" spans="1:12">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="21" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:14">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="7">
+        <v>600</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>20</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M4" s="2">
+        <v>120</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="7">
+        <v>600</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J5" s="5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>20</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M5" s="2">
+        <v>120</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="7">
+        <v>600</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J6" s="5">
+        <v>5</v>
+      </c>
+      <c r="K6" s="2">
+        <v>20</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M6" s="2">
+        <v>120</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="7">
+        <v>600</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J7" s="5">
+        <v>5</v>
+      </c>
+      <c r="K7" s="2">
+        <v>20</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M7" s="2">
+        <v>120</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="5">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="7">
+        <v>600</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J8" s="5">
+        <v>5</v>
+      </c>
+      <c r="K8" s="2">
+        <v>20</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M8" s="2">
+        <v>120</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="5">
+        <v>6</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="7">
+        <v>600</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J9" s="5">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2">
+        <v>20</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M9" s="2">
+        <v>120</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="5">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="5">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="7">
+        <v>600</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J10" s="5">
+        <v>5</v>
+      </c>
+      <c r="K10" s="2">
+        <v>20</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M10" s="2">
+        <v>120</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="5">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="5">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="7">
+        <v>600</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J11" s="5">
+        <v>5</v>
+      </c>
+      <c r="K11" s="2">
+        <v>20</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M11" s="2">
+        <v>120</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12" s="5">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="5">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="7">
+        <v>600</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J12" s="5">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2">
+        <v>20</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M12" s="2">
+        <v>120</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="5">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="7">
+        <v>600</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J13" s="5">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2">
+        <v>20</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M13" s="2">
+        <v>120</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="21" spans="1:10">
-      <c r="A3" s="1" t="s">
+    <row r="14" spans="2:14">
+      <c r="B14" s="5">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="C14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="5">
+        <v>11</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="7">
+        <v>600</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J14" s="5">
+        <v>5</v>
+      </c>
+      <c r="K14" s="2">
+        <v>20</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M14" s="2">
+        <v>120</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" s="5">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="5">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="7">
+        <v>600</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J15" s="5">
+        <v>5</v>
+      </c>
+      <c r="K15" s="2">
+        <v>20</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M15" s="2">
+        <v>120</v>
+      </c>
+      <c r="N15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" s="5">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="5">
+        <v>13</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="7">
+        <v>600</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J16" s="5">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2">
+        <v>20</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M16" s="2">
+        <v>120</v>
+      </c>
+      <c r="N16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="5">
         <v>14</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="5">
+        <v>14</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="7">
+        <v>600</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J17" s="5">
+        <v>5</v>
+      </c>
+      <c r="K17" s="2">
+        <v>20</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M17" s="2">
+        <v>120</v>
+      </c>
+      <c r="N17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="5">
         <v>15</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="C18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="5">
+        <v>15</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="7">
+        <v>600</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J18" s="5">
+        <v>5</v>
+      </c>
+      <c r="K18" s="2">
+        <v>20</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M18" s="2">
+        <v>120</v>
+      </c>
+      <c r="N18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="5">
         <v>16</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="C19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="5">
+        <v>16</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="7">
+        <v>600</v>
+      </c>
+      <c r="I19" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J19" s="5">
+        <v>5</v>
+      </c>
+      <c r="K19" s="2">
+        <v>20</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M19" s="2">
+        <v>120</v>
+      </c>
+      <c r="N19" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:10">
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    <row r="20" spans="2:14">
+      <c r="B20" s="5">
         <v>17</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="2:10">
-      <c r="B5" s="6">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="C20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="5">
+        <v>17</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="7">
+        <v>600</v>
+      </c>
+      <c r="I20" s="5">
+        <v>1101</v>
+      </c>
+      <c r="J20" s="5">
+        <v>5</v>
+      </c>
+      <c r="K20" s="2">
         <v>20</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="6">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="6">
-        <v>3</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="6">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="6">
-        <v>4</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="6">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="6">
-        <v>5</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="6">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="6">
-        <v>6</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="6">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="6">
-        <v>7</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="6">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="6">
-        <v>8</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="6">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="6">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="6">
-        <v>10</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="6">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="6">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="6">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>1</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="6">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="6">
-        <v>12</v>
-      </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="6">
-        <v>13</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="6">
-        <v>13</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="6">
-        <v>14</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="6">
-        <v>14</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="6">
-        <v>15</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="6">
-        <v>15</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="6">
-        <v>16</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="6">
-        <v>16</v>
-      </c>
-      <c r="F19" s="6">
-        <v>1</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="6">
-        <v>17</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="6">
-        <v>17</v>
-      </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>67</v>
+      <c r="L20" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M20" s="2">
+        <v>120</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Packages/cn.etetet.twsmap/Luban/Config/Datas/GameLevel.xlsx
+++ b/Packages/cn.etetet.twsmap/Luban/Config/Datas/GameLevel.xlsx
@@ -101,10 +101,10 @@
     <t>总时间/s</t>
   </si>
   <si>
-    <t>怪物数据配置</t>
-  </si>
-  <si>
-    <t>最终Boss配置</t>
+    <t>怪物数据配置（Id，间隔，数量）</t>
+  </si>
+  <si>
+    <t>最终Boss配置（Id，间隔，数量）</t>
   </si>
   <si>
     <t>疯狂街区</t>
@@ -890,27 +890,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1241,8 +1239,8 @@
     <col min="6" max="6" width="32.25" style="2" customWidth="1"/>
     <col min="7" max="8" width="22.375" style="2" customWidth="1"/>
     <col min="9" max="9" width="7.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="24.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.25" style="2" customWidth="1"/>
     <col min="12" max="14" width="18.875" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
@@ -1272,11 +1270,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1306,11 +1304,11 @@
       <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="1" t="s">
         <v>16</v>
       </c>
@@ -1340,11 +1338,11 @@
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1356,7 +1354,7 @@
       <c r="C4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="5">
@@ -1365,14 +1363,14 @@
       <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>600</v>
       </c>
       <c r="I4" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J4" s="5">
         <v>5</v>
@@ -1381,7 +1379,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="2">
-        <v>1102</v>
+        <v>2002</v>
       </c>
       <c r="M4" s="2">
         <v>120</v>
@@ -1397,7 +1395,7 @@
       <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="5">
@@ -1406,14 +1404,14 @@
       <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>600</v>
       </c>
       <c r="I5" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J5" s="5">
         <v>5</v>
@@ -1422,7 +1420,7 @@
         <v>20</v>
       </c>
       <c r="L5" s="2">
-        <v>1102</v>
+        <v>2003</v>
       </c>
       <c r="M5" s="2">
         <v>120</v>
@@ -1438,7 +1436,7 @@
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="5">
@@ -1447,14 +1445,14 @@
       <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>600</v>
       </c>
       <c r="I6" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J6" s="5">
         <v>5</v>
@@ -1463,7 +1461,7 @@
         <v>20</v>
       </c>
       <c r="L6" s="2">
-        <v>1102</v>
+        <v>2004</v>
       </c>
       <c r="M6" s="2">
         <v>120</v>
@@ -1479,7 +1477,7 @@
       <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E7" s="5">
@@ -1488,14 +1486,14 @@
       <c r="F7" s="5">
         <v>1</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>600</v>
       </c>
       <c r="I7" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J7" s="5">
         <v>5</v>
@@ -1504,7 +1502,7 @@
         <v>20</v>
       </c>
       <c r="L7" s="2">
-        <v>1102</v>
+        <v>2005</v>
       </c>
       <c r="M7" s="2">
         <v>120</v>
@@ -1529,14 +1527,14 @@
       <c r="F8" s="5">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>600</v>
       </c>
       <c r="I8" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J8" s="5">
         <v>5</v>
@@ -1545,7 +1543,7 @@
         <v>20</v>
       </c>
       <c r="L8" s="2">
-        <v>1102</v>
+        <v>2006</v>
       </c>
       <c r="M8" s="2">
         <v>120</v>
@@ -1570,14 +1568,14 @@
       <c r="F9" s="5">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>600</v>
       </c>
       <c r="I9" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J9" s="5">
         <v>5</v>
@@ -1586,7 +1584,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="2">
-        <v>1102</v>
+        <v>2007</v>
       </c>
       <c r="M9" s="2">
         <v>120</v>
@@ -1611,14 +1609,14 @@
       <c r="F10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>600</v>
       </c>
       <c r="I10" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J10" s="5">
         <v>5</v>
@@ -1627,7 +1625,7 @@
         <v>20</v>
       </c>
       <c r="L10" s="2">
-        <v>1102</v>
+        <v>2008</v>
       </c>
       <c r="M10" s="2">
         <v>120</v>
@@ -1652,14 +1650,14 @@
       <c r="F11" s="5">
         <v>1</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>600</v>
       </c>
       <c r="I11" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J11" s="5">
         <v>5</v>
@@ -1668,7 +1666,7 @@
         <v>20</v>
       </c>
       <c r="L11" s="2">
-        <v>1102</v>
+        <v>2009</v>
       </c>
       <c r="M11" s="2">
         <v>120</v>
@@ -1693,14 +1691,14 @@
       <c r="F12" s="5">
         <v>1</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>600</v>
       </c>
       <c r="I12" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J12" s="5">
         <v>5</v>
@@ -1709,7 +1707,7 @@
         <v>20</v>
       </c>
       <c r="L12" s="2">
-        <v>1102</v>
+        <v>2010</v>
       </c>
       <c r="M12" s="2">
         <v>120</v>
@@ -1734,14 +1732,14 @@
       <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>600</v>
       </c>
       <c r="I13" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J13" s="5">
         <v>5</v>
@@ -1750,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="L13" s="2">
-        <v>1102</v>
+        <v>2011</v>
       </c>
       <c r="M13" s="2">
         <v>120</v>
@@ -1775,14 +1773,14 @@
       <c r="F14" s="5">
         <v>1</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>600</v>
       </c>
       <c r="I14" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J14" s="5">
         <v>5</v>
@@ -1791,7 +1789,7 @@
         <v>20</v>
       </c>
       <c r="L14" s="2">
-        <v>1102</v>
+        <v>2012</v>
       </c>
       <c r="M14" s="2">
         <v>120</v>
@@ -1816,14 +1814,14 @@
       <c r="F15" s="5">
         <v>1</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>600</v>
       </c>
       <c r="I15" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J15" s="5">
         <v>5</v>
@@ -1832,7 +1830,7 @@
         <v>20</v>
       </c>
       <c r="L15" s="2">
-        <v>1102</v>
+        <v>2013</v>
       </c>
       <c r="M15" s="2">
         <v>120</v>
@@ -1857,14 +1855,14 @@
       <c r="F16" s="5">
         <v>1</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>600</v>
       </c>
       <c r="I16" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J16" s="5">
         <v>5</v>
@@ -1873,7 +1871,7 @@
         <v>20</v>
       </c>
       <c r="L16" s="2">
-        <v>1102</v>
+        <v>2014</v>
       </c>
       <c r="M16" s="2">
         <v>120</v>
@@ -1898,14 +1896,14 @@
       <c r="F17" s="5">
         <v>1</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>600</v>
       </c>
       <c r="I17" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J17" s="5">
         <v>5</v>
@@ -1914,7 +1912,7 @@
         <v>20</v>
       </c>
       <c r="L17" s="2">
-        <v>1102</v>
+        <v>2015</v>
       </c>
       <c r="M17" s="2">
         <v>120</v>
@@ -1939,14 +1937,14 @@
       <c r="F18" s="5">
         <v>1</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>600</v>
       </c>
       <c r="I18" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J18" s="5">
         <v>5</v>
@@ -1955,7 +1953,7 @@
         <v>20</v>
       </c>
       <c r="L18" s="2">
-        <v>1102</v>
+        <v>2016</v>
       </c>
       <c r="M18" s="2">
         <v>120</v>
@@ -1980,14 +1978,14 @@
       <c r="F19" s="5">
         <v>1</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>600</v>
       </c>
       <c r="I19" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J19" s="5">
         <v>5</v>
@@ -1996,7 +1994,7 @@
         <v>20</v>
       </c>
       <c r="L19" s="2">
-        <v>1102</v>
+        <v>2017</v>
       </c>
       <c r="M19" s="2">
         <v>120</v>
@@ -2021,14 +2019,14 @@
       <c r="F20" s="5">
         <v>1</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>600</v>
       </c>
       <c r="I20" s="5">
-        <v>1101</v>
+        <v>2001</v>
       </c>
       <c r="J20" s="5">
         <v>5</v>
@@ -2037,7 +2035,7 @@
         <v>20</v>
       </c>
       <c r="L20" s="2">
-        <v>1102</v>
+        <v>2018</v>
       </c>
       <c r="M20" s="2">
         <v>120</v>
